--- a/Team-Data/2007-08/2-1-2007-08.xlsx
+++ b/Team-Data/2007-08/2-1-2007-08.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -742,7 +809,7 @@
         <v>29</v>
       </c>
       <c r="AE2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AF2" t="n">
         <v>17</v>
@@ -772,7 +839,7 @@
         <v>29</v>
       </c>
       <c r="AO2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AP2" t="n">
         <v>6</v>
@@ -781,7 +848,7 @@
         <v>8</v>
       </c>
       <c r="AR2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AS2" t="n">
         <v>20</v>
@@ -790,10 +857,10 @@
         <v>12</v>
       </c>
       <c r="AU2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AV2" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AW2" t="n">
         <v>7</v>
@@ -811,7 +878,7 @@
         <v>10</v>
       </c>
       <c r="BB2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BC2" t="n">
         <v>17</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>2-1-2007-08</t>
+          <t>2008-02-01</t>
         </is>
       </c>
     </row>
@@ -921,7 +988,7 @@
         <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -933,7 +1000,7 @@
         <v>1</v>
       </c>
       <c r="AH3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI3" t="n">
         <v>25</v>
@@ -945,13 +1012,13 @@
         <v>5</v>
       </c>
       <c r="AL3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AM3" t="n">
         <v>11</v>
       </c>
       <c r="AN3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AO3" t="n">
         <v>8</v>
@@ -960,7 +1027,7 @@
         <v>7</v>
       </c>
       <c r="AQ3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AR3" t="n">
         <v>26</v>
@@ -972,7 +1039,7 @@
         <v>19</v>
       </c>
       <c r="AU3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AV3" t="n">
         <v>16</v>
@@ -981,13 +1048,13 @@
         <v>4</v>
       </c>
       <c r="AX3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AY3" t="n">
         <v>12</v>
       </c>
       <c r="AZ3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BA3" t="n">
         <v>7</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>2-1-2007-08</t>
+          <t>2008-02-01</t>
         </is>
       </c>
     </row>
@@ -1025,16 +1092,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E4" t="n">
         <v>18</v>
       </c>
       <c r="F4" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G4" t="n">
-        <v>0.383</v>
+        <v>0.391</v>
       </c>
       <c r="H4" t="n">
         <v>48.5</v>
@@ -1043,10 +1110,10 @@
         <v>35.6</v>
       </c>
       <c r="J4" t="n">
-        <v>79.3</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>0.449</v>
+        <v>0.45</v>
       </c>
       <c r="L4" t="n">
         <v>6.2</v>
@@ -1055,10 +1122,10 @@
         <v>17.3</v>
       </c>
       <c r="N4" t="n">
-        <v>0.357</v>
+        <v>0.361</v>
       </c>
       <c r="O4" t="n">
-        <v>17.9</v>
+        <v>17.8</v>
       </c>
       <c r="P4" t="n">
         <v>25.4</v>
@@ -1067,22 +1134,22 @@
         <v>0.704</v>
       </c>
       <c r="R4" t="n">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="S4" t="n">
         <v>29.4</v>
       </c>
       <c r="T4" t="n">
-        <v>40.3</v>
+        <v>40.2</v>
       </c>
       <c r="U4" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="V4" t="n">
         <v>15.2</v>
       </c>
       <c r="W4" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="X4" t="n">
         <v>5</v>
@@ -1094,16 +1161,16 @@
         <v>22.6</v>
       </c>
       <c r="AA4" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="AB4" t="n">
         <v>95.3</v>
       </c>
       <c r="AC4" t="n">
-        <v>-4.3</v>
+        <v>-3.7</v>
       </c>
       <c r="AD4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE4" t="n">
         <v>21</v>
@@ -1121,7 +1188,7 @@
         <v>23</v>
       </c>
       <c r="AJ4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK4" t="n">
         <v>17</v>
@@ -1133,10 +1200,10 @@
         <v>16</v>
       </c>
       <c r="AN4" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AP4" t="n">
         <v>15</v>
@@ -1148,22 +1215,22 @@
         <v>19</v>
       </c>
       <c r="AS4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AT4" t="n">
         <v>27</v>
       </c>
       <c r="AU4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AV4" t="n">
         <v>18</v>
       </c>
       <c r="AW4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AX4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AY4" t="n">
         <v>28</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>2-1-2007-08</t>
+          <t>2008-02-01</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1352,7 @@
         <v>-3</v>
       </c>
       <c r="AD5" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AE5" t="n">
         <v>21</v>
@@ -1315,7 +1382,7 @@
         <v>24</v>
       </c>
       <c r="AN5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AO5" t="n">
         <v>23</v>
@@ -1324,7 +1391,7 @@
         <v>21</v>
       </c>
       <c r="AQ5" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AR5" t="n">
         <v>1</v>
@@ -1336,7 +1403,7 @@
         <v>7</v>
       </c>
       <c r="AU5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AV5" t="n">
         <v>10</v>
@@ -1345,7 +1412,7 @@
         <v>13</v>
       </c>
       <c r="AX5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AY5" t="n">
         <v>27</v>
@@ -1357,7 +1424,7 @@
         <v>16</v>
       </c>
       <c r="BB5" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="BC5" t="n">
         <v>21</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>2-1-2007-08</t>
+          <t>2008-02-01</t>
         </is>
       </c>
     </row>
@@ -1467,22 +1534,22 @@
         <v>-0.9</v>
       </c>
       <c r="AD6" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AE6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AF6" t="n">
         <v>13</v>
       </c>
       <c r="AG6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH6" t="n">
         <v>1</v>
       </c>
       <c r="AI6" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AJ6" t="n">
         <v>9</v>
@@ -1497,16 +1564,16 @@
         <v>12</v>
       </c>
       <c r="AN6" t="n">
+        <v>15</v>
+      </c>
+      <c r="AO6" t="n">
         <v>16</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>15</v>
       </c>
       <c r="AP6" t="n">
         <v>16</v>
       </c>
       <c r="AQ6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AR6" t="n">
         <v>3</v>
@@ -1518,7 +1585,7 @@
         <v>5</v>
       </c>
       <c r="AU6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AV6" t="n">
         <v>11</v>
@@ -1527,7 +1594,7 @@
         <v>9</v>
       </c>
       <c r="AX6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AY6" t="n">
         <v>15</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>2-1-2007-08</t>
+          <t>2008-02-01</t>
         </is>
       </c>
     </row>
@@ -1649,19 +1716,19 @@
         <v>4.9</v>
       </c>
       <c r="AD7" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AE7" t="n">
         <v>5</v>
       </c>
       <c r="AF7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG7" t="n">
         <v>5</v>
       </c>
       <c r="AH7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI7" t="n">
         <v>11</v>
@@ -1676,7 +1743,7 @@
         <v>18</v>
       </c>
       <c r="AM7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AN7" t="n">
         <v>17</v>
@@ -1685,7 +1752,7 @@
         <v>6</v>
       </c>
       <c r="AP7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ7" t="n">
         <v>1</v>
@@ -1718,7 +1785,7 @@
         <v>23</v>
       </c>
       <c r="BA7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BB7" t="n">
         <v>9</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>2-1-2007-08</t>
+          <t>2008-02-01</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>2.1</v>
       </c>
       <c r="AD8" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AE8" t="n">
         <v>11</v>
@@ -1840,7 +1907,7 @@
         <v>8</v>
       </c>
       <c r="AG8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AH8" t="n">
         <v>20</v>
@@ -1861,7 +1928,7 @@
         <v>13</v>
       </c>
       <c r="AN8" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AO8" t="n">
         <v>1</v>
@@ -1882,10 +1949,10 @@
         <v>2</v>
       </c>
       <c r="AU8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AV8" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AW8" t="n">
         <v>1</v>
@@ -1894,7 +1961,7 @@
         <v>1</v>
       </c>
       <c r="AY8" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AZ8" t="n">
         <v>15</v>
@@ -1906,7 +1973,7 @@
         <v>4</v>
       </c>
       <c r="BC8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>2-1-2007-08</t>
+          <t>2008-02-01</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>7.3</v>
       </c>
       <c r="AD9" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AE9" t="n">
         <v>2</v>
@@ -2028,7 +2095,7 @@
         <v>27</v>
       </c>
       <c r="AI9" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AJ9" t="n">
         <v>19</v>
@@ -2043,10 +2110,10 @@
         <v>23</v>
       </c>
       <c r="AN9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AO9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AP9" t="n">
         <v>17</v>
@@ -2055,10 +2122,10 @@
         <v>13</v>
       </c>
       <c r="AR9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AS9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AT9" t="n">
         <v>22</v>
@@ -2070,10 +2137,10 @@
         <v>1</v>
       </c>
       <c r="AW9" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AX9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY9" t="n">
         <v>1</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>2-1-2007-08</t>
+          <t>2008-02-01</t>
         </is>
       </c>
     </row>
@@ -2117,58 +2184,58 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E10" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F10" t="n">
         <v>19</v>
       </c>
       <c r="G10" t="n">
-        <v>0.604</v>
+        <v>0.596</v>
       </c>
       <c r="H10" t="n">
         <v>48.3</v>
       </c>
       <c r="I10" t="n">
-        <v>40.3</v>
+        <v>40.1</v>
       </c>
       <c r="J10" t="n">
-        <v>88.40000000000001</v>
+        <v>88.5</v>
       </c>
       <c r="K10" t="n">
-        <v>0.455</v>
+        <v>0.454</v>
       </c>
       <c r="L10" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>27.6</v>
+        <v>27.8</v>
       </c>
       <c r="N10" t="n">
-        <v>0.357</v>
+        <v>0.354</v>
       </c>
       <c r="O10" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="P10" t="n">
-        <v>25.8</v>
+        <v>25.7</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.75</v>
+        <v>0.748</v>
       </c>
       <c r="R10" t="n">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="S10" t="n">
-        <v>30.1</v>
+        <v>30</v>
       </c>
       <c r="T10" t="n">
         <v>42.2</v>
       </c>
       <c r="U10" t="n">
-        <v>23.1</v>
+        <v>22.9</v>
       </c>
       <c r="V10" t="n">
         <v>13.5</v>
@@ -2177,37 +2244,37 @@
         <v>8.9</v>
       </c>
       <c r="X10" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Y10" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Z10" t="n">
-        <v>23.3</v>
+        <v>23.4</v>
       </c>
       <c r="AA10" t="n">
         <v>22.4</v>
       </c>
       <c r="AB10" t="n">
-        <v>109.6</v>
+        <v>109.3</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="AD10" t="n">
         <v>1</v>
       </c>
       <c r="AE10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF10" t="n">
         <v>11</v>
       </c>
       <c r="AG10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AH10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI10" t="n">
         <v>2</v>
@@ -2216,7 +2283,7 @@
         <v>1</v>
       </c>
       <c r="AK10" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AL10" t="n">
         <v>1</v>
@@ -2225,31 +2292,31 @@
         <v>1</v>
       </c>
       <c r="AN10" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AO10" t="n">
         <v>12</v>
       </c>
       <c r="AP10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ10" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AR10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AS10" t="n">
         <v>18</v>
       </c>
       <c r="AT10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AU10" t="n">
         <v>7</v>
       </c>
       <c r="AV10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW10" t="n">
         <v>3</v>
@@ -2270,7 +2337,7 @@
         <v>1</v>
       </c>
       <c r="BC10" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BD10" t="n">
         <v>10</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>2-1-2007-08</t>
+          <t>2008-02-01</t>
         </is>
       </c>
     </row>
@@ -2299,16 +2366,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E11" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F11" t="n">
         <v>20</v>
       </c>
       <c r="G11" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.556</v>
       </c>
       <c r="H11" t="n">
         <v>48.2</v>
@@ -2320,43 +2387,43 @@
         <v>81.59999999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>0.444</v>
+        <v>0.443</v>
       </c>
       <c r="L11" t="n">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="M11" t="n">
         <v>19.8</v>
       </c>
       <c r="N11" t="n">
-        <v>0.336</v>
+        <v>0.334</v>
       </c>
       <c r="O11" t="n">
-        <v>16.8</v>
+        <v>16.7</v>
       </c>
       <c r="P11" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.729</v>
+        <v>0.73</v>
       </c>
       <c r="R11" t="n">
-        <v>12.3</v>
+        <v>12.4</v>
       </c>
       <c r="S11" t="n">
-        <v>31.7</v>
+        <v>31.6</v>
       </c>
       <c r="T11" t="n">
         <v>44</v>
       </c>
       <c r="U11" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="V11" t="n">
         <v>14.8</v>
       </c>
       <c r="W11" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="X11" t="n">
         <v>5.5</v>
@@ -2368,16 +2435,16 @@
         <v>20.1</v>
       </c>
       <c r="AA11" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="AB11" t="n">
-        <v>95.90000000000001</v>
+        <v>95.7</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AD11" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AE11" t="n">
         <v>13</v>
@@ -2389,25 +2456,25 @@
         <v>13</v>
       </c>
       <c r="AH11" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AI11" t="n">
         <v>16</v>
       </c>
       <c r="AJ11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AK11" t="n">
         <v>21</v>
       </c>
       <c r="AL11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AM11" t="n">
         <v>8</v>
       </c>
       <c r="AN11" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AO11" t="n">
         <v>26</v>
@@ -2419,7 +2486,7 @@
         <v>22</v>
       </c>
       <c r="AR11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AS11" t="n">
         <v>8</v>
@@ -2428,31 +2495,31 @@
         <v>6</v>
       </c>
       <c r="AU11" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AV11" t="n">
         <v>13</v>
       </c>
       <c r="AW11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AX11" t="n">
         <v>4</v>
       </c>
       <c r="AY11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AZ11" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BA11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB11" t="n">
         <v>20</v>
       </c>
       <c r="BC11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>2-1-2007-08</t>
+          <t>2008-02-01</t>
         </is>
       </c>
     </row>
@@ -2481,16 +2548,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E12" t="n">
         <v>19</v>
       </c>
       <c r="F12" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G12" t="n">
-        <v>0.404</v>
+        <v>0.413</v>
       </c>
       <c r="H12" t="n">
         <v>48.3</v>
@@ -2499,28 +2566,28 @@
         <v>38.1</v>
       </c>
       <c r="J12" t="n">
-        <v>86</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="K12" t="n">
         <v>0.443</v>
       </c>
       <c r="L12" t="n">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="M12" t="n">
         <v>23.9</v>
       </c>
       <c r="N12" t="n">
-        <v>0.366</v>
+        <v>0.363</v>
       </c>
       <c r="O12" t="n">
         <v>18.3</v>
       </c>
       <c r="P12" t="n">
-        <v>24</v>
+        <v>24.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.763</v>
+        <v>0.762</v>
       </c>
       <c r="R12" t="n">
         <v>11.6</v>
@@ -2532,7 +2599,7 @@
         <v>44.6</v>
       </c>
       <c r="U12" t="n">
-        <v>23.3</v>
+        <v>23.2</v>
       </c>
       <c r="V12" t="n">
         <v>16.6</v>
@@ -2544,7 +2611,7 @@
         <v>5</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Z12" t="n">
         <v>24.4</v>
@@ -2559,19 +2626,19 @@
         <v>-1.9</v>
       </c>
       <c r="AD12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AF12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG12" t="n">
         <v>20</v>
       </c>
       <c r="AH12" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AI12" t="n">
         <v>7</v>
@@ -2589,10 +2656,10 @@
         <v>3</v>
       </c>
       <c r="AN12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AO12" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AP12" t="n">
         <v>20</v>
@@ -2619,10 +2686,10 @@
         <v>10</v>
       </c>
       <c r="AX12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AY12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AZ12" t="n">
         <v>29</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>2-1-2007-08</t>
+          <t>2008-02-01</t>
         </is>
       </c>
     </row>
@@ -2663,58 +2730,58 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E13" t="n">
         <v>14</v>
       </c>
       <c r="F13" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G13" t="n">
-        <v>0.326</v>
+        <v>0.333</v>
       </c>
       <c r="H13" t="n">
         <v>48.2</v>
       </c>
       <c r="I13" t="n">
-        <v>34.7</v>
+        <v>34.9</v>
       </c>
       <c r="J13" t="n">
-        <v>79.3</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>0.438</v>
+        <v>0.439</v>
       </c>
       <c r="L13" t="n">
         <v>4.2</v>
       </c>
       <c r="M13" t="n">
-        <v>12.7</v>
+        <v>12.9</v>
       </c>
       <c r="N13" t="n">
-        <v>0.328</v>
+        <v>0.33</v>
       </c>
       <c r="O13" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="P13" t="n">
-        <v>26.4</v>
+        <v>26.3</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.782</v>
+        <v>0.783</v>
       </c>
       <c r="R13" t="n">
         <v>9.6</v>
       </c>
       <c r="S13" t="n">
-        <v>31.3</v>
+        <v>31.4</v>
       </c>
       <c r="T13" t="n">
-        <v>40.9</v>
+        <v>41.1</v>
       </c>
       <c r="U13" t="n">
-        <v>21.5</v>
+        <v>21.8</v>
       </c>
       <c r="V13" t="n">
         <v>14.6</v>
@@ -2723,25 +2790,25 @@
         <v>6.7</v>
       </c>
       <c r="X13" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Y13" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Z13" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="AA13" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="AB13" t="n">
-        <v>94.3</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="AC13" t="n">
-        <v>-4.8</v>
+        <v>-4.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AE13" t="n">
         <v>25</v>
@@ -2753,22 +2820,22 @@
         <v>25</v>
       </c>
       <c r="AH13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI13" t="n">
         <v>28</v>
       </c>
       <c r="AJ13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK13" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL13" t="n">
         <v>27</v>
       </c>
       <c r="AM13" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AN13" t="n">
         <v>28</v>
@@ -2792,7 +2859,7 @@
         <v>21</v>
       </c>
       <c r="AU13" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AV13" t="n">
         <v>12</v>
@@ -2801,22 +2868,22 @@
         <v>22</v>
       </c>
       <c r="AX13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AY13" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AZ13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BA13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BB13" t="n">
         <v>24</v>
       </c>
       <c r="BC13" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BD13" t="n">
         <v>10</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>2-1-2007-08</t>
+          <t>2008-02-01</t>
         </is>
       </c>
     </row>
@@ -2845,43 +2912,43 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E14" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F14" t="n">
         <v>16</v>
       </c>
       <c r="G14" t="n">
-        <v>0.644</v>
+        <v>0.636</v>
       </c>
       <c r="H14" t="n">
         <v>48.1</v>
       </c>
       <c r="I14" t="n">
-        <v>39</v>
+        <v>38.8</v>
       </c>
       <c r="J14" t="n">
-        <v>82</v>
+        <v>81.8</v>
       </c>
       <c r="K14" t="n">
-        <v>0.476</v>
+        <v>0.474</v>
       </c>
       <c r="L14" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="M14" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="N14" t="n">
-        <v>0.369</v>
+        <v>0.367</v>
       </c>
       <c r="O14" t="n">
-        <v>21.9</v>
+        <v>22.2</v>
       </c>
       <c r="P14" t="n">
-        <v>29.2</v>
+        <v>29.6</v>
       </c>
       <c r="Q14" t="n">
         <v>0.749</v>
@@ -2893,46 +2960,46 @@
         <v>33.8</v>
       </c>
       <c r="T14" t="n">
-        <v>44.7</v>
+        <v>44.8</v>
       </c>
       <c r="U14" t="n">
-        <v>23.5</v>
+        <v>23.4</v>
       </c>
       <c r="V14" t="n">
-        <v>15.4</v>
+        <v>15.7</v>
       </c>
       <c r="W14" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="X14" t="n">
         <v>5.2</v>
       </c>
       <c r="Y14" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Z14" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>23.1</v>
+        <v>23.3</v>
       </c>
       <c r="AB14" t="n">
-        <v>107.2</v>
+        <v>106.9</v>
       </c>
       <c r="AC14" t="n">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="AD14" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AE14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF14" t="n">
         <v>6</v>
       </c>
       <c r="AG14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AH14" t="n">
         <v>24</v>
@@ -2947,7 +3014,7 @@
         <v>3</v>
       </c>
       <c r="AL14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AM14" t="n">
         <v>9</v>
@@ -2959,7 +3026,7 @@
         <v>2</v>
       </c>
       <c r="AP14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ14" t="n">
         <v>18</v>
@@ -2974,7 +3041,7 @@
         <v>3</v>
       </c>
       <c r="AU14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AV14" t="n">
         <v>24</v>
@@ -2992,13 +3059,13 @@
         <v>16</v>
       </c>
       <c r="BA14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BB14" t="n">
         <v>3</v>
       </c>
       <c r="BC14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BD14" t="n">
         <v>10</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>2-1-2007-08</t>
+          <t>2008-02-01</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3172,7 @@
         <v>-4.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AE15" t="n">
         <v>27</v>
@@ -3117,7 +3184,7 @@
         <v>27</v>
       </c>
       <c r="AH15" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AI15" t="n">
         <v>10</v>
@@ -3138,7 +3205,7 @@
         <v>8</v>
       </c>
       <c r="AO15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AP15" t="n">
         <v>18</v>
@@ -3180,7 +3247,7 @@
         <v>8</v>
       </c>
       <c r="BC15" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BD15" t="n">
         <v>10</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>2-1-2007-08</t>
+          <t>2008-02-01</t>
         </is>
       </c>
     </row>
@@ -3209,22 +3276,22 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E16" t="n">
         <v>9</v>
       </c>
       <c r="F16" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G16" t="n">
-        <v>0.196</v>
+        <v>0.2</v>
       </c>
       <c r="H16" t="n">
         <v>48.3</v>
       </c>
       <c r="I16" t="n">
-        <v>35.1</v>
+        <v>35.2</v>
       </c>
       <c r="J16" t="n">
         <v>77.2</v>
@@ -3239,22 +3306,22 @@
         <v>13.7</v>
       </c>
       <c r="N16" t="n">
-        <v>0.337</v>
+        <v>0.339</v>
       </c>
       <c r="O16" t="n">
         <v>18.2</v>
       </c>
       <c r="P16" t="n">
-        <v>25.7</v>
+        <v>25.8</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.708</v>
+        <v>0.705</v>
       </c>
       <c r="R16" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="S16" t="n">
-        <v>29.2</v>
+        <v>29.1</v>
       </c>
       <c r="T16" t="n">
         <v>38.4</v>
@@ -3263,52 +3330,52 @@
         <v>19.7</v>
       </c>
       <c r="V16" t="n">
-        <v>14.9</v>
+        <v>14.8</v>
       </c>
       <c r="W16" t="n">
         <v>7.3</v>
       </c>
       <c r="X16" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Y16" t="n">
         <v>3.8</v>
       </c>
       <c r="Z16" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="AA16" t="n">
         <v>22</v>
       </c>
       <c r="AB16" t="n">
-        <v>93</v>
+        <v>93.2</v>
       </c>
       <c r="AC16" t="n">
-        <v>-7.1</v>
+        <v>-7</v>
       </c>
       <c r="AD16" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AE16" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AF16" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AG16" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AH16" t="n">
         <v>12</v>
       </c>
       <c r="AI16" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AJ16" t="n">
         <v>29</v>
       </c>
       <c r="AK16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AL16" t="n">
         <v>25</v>
@@ -3317,16 +3384,16 @@
         <v>25</v>
       </c>
       <c r="AN16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AO16" t="n">
         <v>18</v>
       </c>
       <c r="AP16" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AQ16" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AR16" t="n">
         <v>29</v>
@@ -3338,7 +3405,7 @@
         <v>30</v>
       </c>
       <c r="AU16" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AV16" t="n">
         <v>14</v>
@@ -3347,7 +3414,7 @@
         <v>19</v>
       </c>
       <c r="AX16" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AY16" t="n">
         <v>3</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>2-1-2007-08</t>
+          <t>2008-02-01</t>
         </is>
       </c>
     </row>
@@ -3469,37 +3536,37 @@
         <v>-6.8</v>
       </c>
       <c r="AD17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE17" t="n">
         <v>21</v>
       </c>
       <c r="AF17" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AG17" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AH17" t="n">
         <v>10</v>
       </c>
       <c r="AI17" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AJ17" t="n">
+        <v>17</v>
+      </c>
+      <c r="AK17" t="n">
         <v>18</v>
       </c>
-      <c r="AK17" t="n">
-        <v>19</v>
-      </c>
       <c r="AL17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AM17" t="n">
         <v>21</v>
       </c>
       <c r="AN17" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO17" t="n">
         <v>27</v>
@@ -3511,7 +3578,7 @@
         <v>21</v>
       </c>
       <c r="AR17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AS17" t="n">
         <v>30</v>
@@ -3523,13 +3590,13 @@
         <v>16</v>
       </c>
       <c r="AV17" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AW17" t="n">
         <v>21</v>
       </c>
       <c r="AX17" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AY17" t="n">
         <v>23</v>
@@ -3538,7 +3605,7 @@
         <v>20</v>
       </c>
       <c r="BA17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BB17" t="n">
         <v>25</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>2-1-2007-08</t>
+          <t>2008-02-01</t>
         </is>
       </c>
     </row>
@@ -3573,70 +3640,70 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F18" t="n">
         <v>36</v>
       </c>
       <c r="G18" t="n">
-        <v>0.217</v>
+        <v>0.2</v>
       </c>
       <c r="H18" t="n">
         <v>48</v>
       </c>
       <c r="I18" t="n">
-        <v>36.6</v>
+        <v>36.4</v>
       </c>
       <c r="J18" t="n">
-        <v>83.3</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>0.44</v>
+        <v>0.439</v>
       </c>
       <c r="L18" t="n">
         <v>5.5</v>
       </c>
       <c r="M18" t="n">
-        <v>16.3</v>
+        <v>16.4</v>
       </c>
       <c r="N18" t="n">
-        <v>0.335</v>
+        <v>0.336</v>
       </c>
       <c r="O18" t="n">
-        <v>15.2</v>
+        <v>15.3</v>
       </c>
       <c r="P18" t="n">
-        <v>21</v>
+        <v>21.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.724</v>
+        <v>0.723</v>
       </c>
       <c r="R18" t="n">
         <v>12.4</v>
       </c>
       <c r="S18" t="n">
-        <v>29.7</v>
+        <v>29.6</v>
       </c>
       <c r="T18" t="n">
-        <v>42.2</v>
+        <v>42</v>
       </c>
       <c r="U18" t="n">
         <v>18.9</v>
       </c>
       <c r="V18" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="W18" t="n">
         <v>7.4</v>
       </c>
       <c r="X18" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="Y18" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="Z18" t="n">
         <v>23.7</v>
@@ -3645,13 +3712,13 @@
         <v>18.1</v>
       </c>
       <c r="AB18" t="n">
-        <v>94</v>
+        <v>93.7</v>
       </c>
       <c r="AC18" t="n">
-        <v>-7.3</v>
+        <v>-8</v>
       </c>
       <c r="AD18" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AE18" t="n">
         <v>29</v>
@@ -3666,13 +3733,13 @@
         <v>29</v>
       </c>
       <c r="AI18" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AJ18" t="n">
         <v>8</v>
       </c>
       <c r="AK18" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AL18" t="n">
         <v>23</v>
@@ -3681,40 +3748,40 @@
         <v>22</v>
       </c>
       <c r="AN18" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO18" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AP18" t="n">
         <v>28</v>
       </c>
       <c r="AQ18" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AR18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AS18" t="n">
         <v>22</v>
       </c>
       <c r="AT18" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AU18" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AV18" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AW18" t="n">
         <v>18</v>
       </c>
       <c r="AX18" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AY18" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AZ18" t="n">
         <v>28</v>
@@ -3723,10 +3790,10 @@
         <v>29</v>
       </c>
       <c r="BB18" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BC18" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BD18" t="n">
         <v>10</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>2-1-2007-08</t>
+          <t>2008-02-01</t>
         </is>
       </c>
     </row>
@@ -3755,22 +3822,22 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E19" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F19" t="n">
         <v>26</v>
       </c>
       <c r="G19" t="n">
-        <v>0.435</v>
+        <v>0.422</v>
       </c>
       <c r="H19" t="n">
         <v>48.4</v>
       </c>
       <c r="I19" t="n">
-        <v>33.7</v>
+        <v>33.6</v>
       </c>
       <c r="J19" t="n">
         <v>77.8</v>
@@ -3782,7 +3849,7 @@
         <v>5.6</v>
       </c>
       <c r="M19" t="n">
-        <v>16.9</v>
+        <v>17</v>
       </c>
       <c r="N19" t="n">
         <v>0.332</v>
@@ -3791,16 +3858,16 @@
         <v>20.7</v>
       </c>
       <c r="P19" t="n">
-        <v>28.9</v>
+        <v>29</v>
       </c>
       <c r="Q19" t="n">
         <v>0.714</v>
       </c>
       <c r="R19" t="n">
-        <v>11.9</v>
+        <v>12</v>
       </c>
       <c r="S19" t="n">
-        <v>30.5</v>
+        <v>30.4</v>
       </c>
       <c r="T19" t="n">
         <v>42.4</v>
@@ -3821,19 +3888,19 @@
         <v>4.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="AA19" t="n">
-        <v>23.2</v>
+        <v>23.3</v>
       </c>
       <c r="AB19" t="n">
-        <v>93.7</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="AC19" t="n">
-        <v>-5.6</v>
+        <v>-5.9</v>
       </c>
       <c r="AD19" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AE19" t="n">
         <v>18</v>
@@ -3845,7 +3912,7 @@
         <v>19</v>
       </c>
       <c r="AH19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI19" t="n">
         <v>30</v>
@@ -3860,7 +3927,7 @@
         <v>20</v>
       </c>
       <c r="AM19" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AN19" t="n">
         <v>25</v>
@@ -3878,7 +3945,7 @@
         <v>11</v>
       </c>
       <c r="AS19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AT19" t="n">
         <v>11</v>
@@ -3887,7 +3954,7 @@
         <v>3</v>
       </c>
       <c r="AV19" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AW19" t="n">
         <v>25</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>2-1-2007-08</t>
+          <t>2008-02-01</t>
         </is>
       </c>
     </row>
@@ -3937,16 +4004,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E20" t="n">
         <v>32</v>
       </c>
       <c r="F20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G20" t="n">
-        <v>0.696</v>
+        <v>0.711</v>
       </c>
       <c r="H20" t="n">
         <v>48.3</v>
@@ -3955,19 +4022,19 @@
         <v>38.2</v>
       </c>
       <c r="J20" t="n">
-        <v>83.5</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="K20" t="n">
         <v>0.458</v>
       </c>
       <c r="L20" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="M20" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="N20" t="n">
-        <v>0.379</v>
+        <v>0.375</v>
       </c>
       <c r="O20" t="n">
         <v>15.3</v>
@@ -3976,22 +4043,22 @@
         <v>19.6</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.78</v>
+        <v>0.781</v>
       </c>
       <c r="R20" t="n">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="S20" t="n">
         <v>31.3</v>
       </c>
       <c r="T20" t="n">
-        <v>43</v>
+        <v>43.1</v>
       </c>
       <c r="U20" t="n">
         <v>21.7</v>
       </c>
       <c r="V20" t="n">
-        <v>12.3</v>
+        <v>12.2</v>
       </c>
       <c r="W20" t="n">
         <v>7.5</v>
@@ -4009,22 +4076,22 @@
         <v>18.7</v>
       </c>
       <c r="AB20" t="n">
-        <v>99.5</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="AC20" t="n">
-        <v>6.1</v>
+        <v>6.4</v>
       </c>
       <c r="AD20" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AE20" t="n">
         <v>4</v>
       </c>
       <c r="AF20" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG20" t="n">
         <v>3</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>4</v>
       </c>
       <c r="AH20" t="n">
         <v>12</v>
@@ -4039,13 +4106,13 @@
         <v>11</v>
       </c>
       <c r="AL20" t="n">
+        <v>8</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>7</v>
+      </c>
+      <c r="AN20" t="n">
         <v>6</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>6</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>4</v>
       </c>
       <c r="AO20" t="n">
         <v>29</v>
@@ -4057,7 +4124,7 @@
         <v>7</v>
       </c>
       <c r="AR20" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AS20" t="n">
         <v>12</v>
@@ -4066,19 +4133,19 @@
         <v>8</v>
       </c>
       <c r="AU20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AV20" t="n">
         <v>3</v>
       </c>
       <c r="AW20" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AX20" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AY20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ20" t="n">
         <v>2</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>2-1-2007-08</t>
+          <t>2008-02-01</t>
         </is>
       </c>
     </row>
@@ -4119,28 +4186,28 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E21" t="n">
         <v>14</v>
       </c>
       <c r="F21" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G21" t="n">
-        <v>0.304</v>
+        <v>0.311</v>
       </c>
       <c r="H21" t="n">
-        <v>48.3</v>
+        <v>48.2</v>
       </c>
       <c r="I21" t="n">
-        <v>35.2</v>
+        <v>35.1</v>
       </c>
       <c r="J21" t="n">
-        <v>80.3</v>
+        <v>80</v>
       </c>
       <c r="K21" t="n">
-        <v>0.438</v>
+        <v>0.439</v>
       </c>
       <c r="L21" t="n">
         <v>5.6</v>
@@ -4149,55 +4216,55 @@
         <v>16.8</v>
       </c>
       <c r="N21" t="n">
-        <v>0.331</v>
+        <v>0.336</v>
       </c>
       <c r="O21" t="n">
-        <v>18.7</v>
+        <v>18.9</v>
       </c>
       <c r="P21" t="n">
-        <v>26</v>
+        <v>26.3</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.719</v>
+        <v>0.718</v>
       </c>
       <c r="R21" t="n">
-        <v>12.6</v>
+        <v>12.5</v>
       </c>
       <c r="S21" t="n">
-        <v>29.4</v>
+        <v>29.2</v>
       </c>
       <c r="T21" t="n">
-        <v>42</v>
+        <v>41.7</v>
       </c>
       <c r="U21" t="n">
-        <v>18.2</v>
+        <v>18.4</v>
       </c>
       <c r="V21" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="W21" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="X21" t="n">
         <v>2.3</v>
       </c>
       <c r="Y21" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Z21" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="AA21" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="AB21" t="n">
-        <v>94.59999999999999</v>
+        <v>94.7</v>
       </c>
       <c r="AC21" t="n">
         <v>-6.1</v>
       </c>
       <c r="AD21" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AE21" t="n">
         <v>25</v>
@@ -4209,31 +4276,31 @@
         <v>26</v>
       </c>
       <c r="AH21" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AI21" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AJ21" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AK21" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AL21" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AM21" t="n">
         <v>19</v>
       </c>
       <c r="AN21" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AO21" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AP21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AQ21" t="n">
         <v>26</v>
@@ -4242,7 +4309,7 @@
         <v>4</v>
       </c>
       <c r="AS21" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AT21" t="n">
         <v>17</v>
@@ -4251,10 +4318,10 @@
         <v>30</v>
       </c>
       <c r="AV21" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW21" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AX21" t="n">
         <v>30</v>
@@ -4269,7 +4336,7 @@
         <v>15</v>
       </c>
       <c r="BB21" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BC21" t="n">
         <v>26</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>2-1-2007-08</t>
+          <t>2008-02-01</t>
         </is>
       </c>
     </row>
@@ -4301,46 +4368,46 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E22" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F22" t="n">
         <v>18</v>
       </c>
       <c r="G22" t="n">
-        <v>0.625</v>
+        <v>0.617</v>
       </c>
       <c r="H22" t="n">
         <v>48.4</v>
       </c>
       <c r="I22" t="n">
-        <v>36.6</v>
+        <v>36.5</v>
       </c>
       <c r="J22" t="n">
         <v>78.40000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>0.467</v>
+        <v>0.465</v>
       </c>
       <c r="L22" t="n">
         <v>8.9</v>
       </c>
       <c r="M22" t="n">
-        <v>24.7</v>
+        <v>24.6</v>
       </c>
       <c r="N22" t="n">
-        <v>0.362</v>
+        <v>0.363</v>
       </c>
       <c r="O22" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="P22" t="n">
-        <v>29.4</v>
+        <v>29.5</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.726</v>
+        <v>0.725</v>
       </c>
       <c r="R22" t="n">
         <v>9.800000000000001</v>
@@ -4358,13 +4425,13 @@
         <v>15</v>
       </c>
       <c r="W22" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="X22" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Y22" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Z22" t="n">
         <v>21.1</v>
@@ -4373,10 +4440,10 @@
         <v>24.1</v>
       </c>
       <c r="AB22" t="n">
-        <v>103.4</v>
+        <v>103.3</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="AD22" t="n">
         <v>1</v>
@@ -4391,13 +4458,13 @@
         <v>8</v>
       </c>
       <c r="AH22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AI22" t="n">
         <v>13</v>
       </c>
       <c r="AJ22" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK22" t="n">
         <v>6</v>
@@ -4415,7 +4482,7 @@
         <v>7</v>
       </c>
       <c r="AP22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ22" t="n">
         <v>23</v>
@@ -4436,7 +4503,7 @@
         <v>15</v>
       </c>
       <c r="AW22" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AX22" t="n">
         <v>17</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>2-1-2007-08</t>
+          <t>2008-02-01</t>
         </is>
       </c>
     </row>
@@ -4483,37 +4550,37 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E23" t="n">
         <v>18</v>
       </c>
       <c r="F23" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G23" t="n">
-        <v>0.383</v>
+        <v>0.391</v>
       </c>
       <c r="H23" t="n">
         <v>48.2</v>
       </c>
       <c r="I23" t="n">
-        <v>36.1</v>
+        <v>36</v>
       </c>
       <c r="J23" t="n">
-        <v>80.40000000000001</v>
+        <v>80.3</v>
       </c>
       <c r="K23" t="n">
-        <v>0.449</v>
+        <v>0.448</v>
       </c>
       <c r="L23" t="n">
         <v>3.7</v>
       </c>
       <c r="M23" t="n">
-        <v>11.7</v>
+        <v>11.8</v>
       </c>
       <c r="N23" t="n">
-        <v>0.317</v>
+        <v>0.316</v>
       </c>
       <c r="O23" t="n">
         <v>18.1</v>
@@ -4528,40 +4595,40 @@
         <v>13.3</v>
       </c>
       <c r="S23" t="n">
-        <v>28.8</v>
+        <v>28.9</v>
       </c>
       <c r="T23" t="n">
-        <v>42</v>
+        <v>42.2</v>
       </c>
       <c r="U23" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="V23" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="W23" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="X23" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="Y23" t="n">
         <v>5</v>
       </c>
       <c r="Z23" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="AA23" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="AB23" t="n">
-        <v>94.09999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="AC23" t="n">
         <v>-2</v>
       </c>
       <c r="AD23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE23" t="n">
         <v>21</v>
@@ -4582,7 +4649,7 @@
         <v>16</v>
       </c>
       <c r="AK23" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AL23" t="n">
         <v>30</v>
@@ -4600,7 +4667,7 @@
         <v>14</v>
       </c>
       <c r="AQ23" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AR23" t="n">
         <v>2</v>
@@ -4609,19 +4676,19 @@
         <v>29</v>
       </c>
       <c r="AT23" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AU23" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AV23" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AW23" t="n">
         <v>6</v>
       </c>
       <c r="AX23" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AY23" t="n">
         <v>17</v>
@@ -4633,7 +4700,7 @@
         <v>19</v>
       </c>
       <c r="BB23" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BC23" t="n">
         <v>19</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>2-1-2007-08</t>
+          <t>2008-02-01</t>
         </is>
       </c>
     </row>
@@ -4743,16 +4810,16 @@
         <v>6</v>
       </c>
       <c r="AD24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE24" t="n">
         <v>2</v>
       </c>
       <c r="AF24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH24" t="n">
         <v>28</v>
@@ -4764,7 +4831,7 @@
         <v>6</v>
       </c>
       <c r="AK24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL24" t="n">
         <v>2</v>
@@ -4791,7 +4858,7 @@
         <v>6</v>
       </c>
       <c r="AT24" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AU24" t="n">
         <v>1</v>
@@ -4800,7 +4867,7 @@
         <v>8</v>
       </c>
       <c r="AW24" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AX24" t="n">
         <v>2</v>
@@ -4812,7 +4879,7 @@
         <v>4</v>
       </c>
       <c r="BA24" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BB24" t="n">
         <v>2</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>2-1-2007-08</t>
+          <t>2008-02-01</t>
         </is>
       </c>
     </row>
@@ -4847,46 +4914,46 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E25" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F25" t="n">
         <v>19</v>
       </c>
       <c r="G25" t="n">
-        <v>0.587</v>
+        <v>0.578</v>
       </c>
       <c r="H25" t="n">
-        <v>48.8</v>
+        <v>48.7</v>
       </c>
       <c r="I25" t="n">
         <v>35.7</v>
       </c>
       <c r="J25" t="n">
-        <v>78.7</v>
+        <v>78.5</v>
       </c>
       <c r="K25" t="n">
-        <v>0.454</v>
+        <v>0.455</v>
       </c>
       <c r="L25" t="n">
         <v>6.8</v>
       </c>
       <c r="M25" t="n">
-        <v>17.5</v>
+        <v>17.4</v>
       </c>
       <c r="N25" t="n">
-        <v>0.39</v>
+        <v>0.392</v>
       </c>
       <c r="O25" t="n">
-        <v>17.9</v>
+        <v>18</v>
       </c>
       <c r="P25" t="n">
-        <v>23.2</v>
+        <v>23.4</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.77</v>
+        <v>0.769</v>
       </c>
       <c r="R25" t="n">
         <v>10.4</v>
@@ -4901,13 +4968,13 @@
         <v>21.4</v>
       </c>
       <c r="V25" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="W25" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="X25" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Y25" t="n">
         <v>3.8</v>
@@ -4916,19 +4983,19 @@
         <v>20.1</v>
       </c>
       <c r="AA25" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="AB25" t="n">
         <v>96.2</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="AD25" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AE25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AF25" t="n">
         <v>11</v>
@@ -4943,10 +5010,10 @@
         <v>22</v>
       </c>
       <c r="AJ25" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AK25" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AL25" t="n">
         <v>11</v>
@@ -4958,16 +5025,16 @@
         <v>2</v>
       </c>
       <c r="AO25" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AP25" t="n">
         <v>22</v>
       </c>
       <c r="AQ25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR25" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS25" t="n">
         <v>21</v>
@@ -4979,13 +5046,13 @@
         <v>14</v>
       </c>
       <c r="AV25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW25" t="n">
         <v>30</v>
       </c>
       <c r="AX25" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AY25" t="n">
         <v>4</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>2-1-2007-08</t>
+          <t>2008-02-01</t>
         </is>
       </c>
     </row>
@@ -5029,85 +5096,85 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E26" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F26" t="n">
         <v>24</v>
       </c>
       <c r="G26" t="n">
-        <v>0.467</v>
+        <v>0.455</v>
       </c>
       <c r="H26" t="n">
         <v>48.2</v>
       </c>
       <c r="I26" t="n">
-        <v>36.2</v>
+        <v>36</v>
       </c>
       <c r="J26" t="n">
-        <v>78.5</v>
+        <v>78.3</v>
       </c>
       <c r="K26" t="n">
-        <v>0.461</v>
+        <v>0.46</v>
       </c>
       <c r="L26" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="M26" t="n">
-        <v>17</v>
+        <v>16.9</v>
       </c>
       <c r="N26" t="n">
-        <v>0.374</v>
+        <v>0.372</v>
       </c>
       <c r="O26" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="P26" t="n">
-        <v>27.3</v>
+        <v>27.4</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.792</v>
+        <v>0.794</v>
       </c>
       <c r="R26" t="n">
         <v>10</v>
       </c>
       <c r="S26" t="n">
-        <v>29.6</v>
+        <v>29.5</v>
       </c>
       <c r="T26" t="n">
-        <v>39.6</v>
+        <v>39.5</v>
       </c>
       <c r="U26" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="V26" t="n">
-        <v>16.4</v>
+        <v>16.5</v>
       </c>
       <c r="W26" t="n">
         <v>8</v>
       </c>
       <c r="X26" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Y26" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Z26" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="AA26" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="AB26" t="n">
-        <v>100.3</v>
+        <v>100</v>
       </c>
       <c r="AC26" t="n">
-        <v>-2</v>
+        <v>-2.3</v>
       </c>
       <c r="AD26" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AE26" t="n">
         <v>17</v>
@@ -5119,13 +5186,13 @@
         <v>17</v>
       </c>
       <c r="AH26" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AI26" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AJ26" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK26" t="n">
         <v>8</v>
@@ -5134,7 +5201,7 @@
         <v>15</v>
       </c>
       <c r="AM26" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AN26" t="n">
         <v>7</v>
@@ -5149,7 +5216,7 @@
         <v>4</v>
       </c>
       <c r="AR26" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AS26" t="n">
         <v>23</v>
@@ -5158,7 +5225,7 @@
         <v>29</v>
       </c>
       <c r="AU26" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AV26" t="n">
         <v>29</v>
@@ -5167,16 +5234,16 @@
         <v>8</v>
       </c>
       <c r="AX26" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AY26" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ26" t="n">
         <v>24</v>
       </c>
       <c r="BA26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BB26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>2-1-2007-08</t>
+          <t>2008-02-01</t>
         </is>
       </c>
     </row>
@@ -5289,10 +5356,10 @@
         <v>4.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AE27" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AF27" t="n">
         <v>6</v>
@@ -5301,25 +5368,25 @@
         <v>6</v>
       </c>
       <c r="AH27" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI27" t="n">
         <v>21</v>
       </c>
       <c r="AJ27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK27" t="n">
         <v>13</v>
       </c>
       <c r="AL27" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AM27" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AN27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AO27" t="n">
         <v>25</v>
@@ -5349,7 +5416,7 @@
         <v>23</v>
       </c>
       <c r="AX27" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AY27" t="n">
         <v>13</v>
@@ -5358,7 +5425,7 @@
         <v>1</v>
       </c>
       <c r="BA27" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BB27" t="n">
         <v>19</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>2-1-2007-08</t>
+          <t>2008-02-01</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>-7.7</v>
       </c>
       <c r="AD28" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AE28" t="n">
         <v>28</v>
@@ -5483,7 +5550,7 @@
         <v>28</v>
       </c>
       <c r="AH28" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AI28" t="n">
         <v>8</v>
@@ -5492,16 +5559,16 @@
         <v>3</v>
       </c>
       <c r="AK28" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AL28" t="n">
         <v>26</v>
       </c>
       <c r="AM28" t="n">
+        <v>27</v>
+      </c>
+      <c r="AN28" t="n">
         <v>26</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>24</v>
       </c>
       <c r="AO28" t="n">
         <v>24</v>
@@ -5531,7 +5598,7 @@
         <v>24</v>
       </c>
       <c r="AX28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AY28" t="n">
         <v>26</v>
@@ -5540,13 +5607,13 @@
         <v>12</v>
       </c>
       <c r="BA28" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BB28" t="n">
         <v>17</v>
       </c>
       <c r="BC28" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BD28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>2-1-2007-08</t>
+          <t>2008-02-01</t>
         </is>
       </c>
     </row>
@@ -5575,16 +5642,16 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E29" t="n">
         <v>25</v>
       </c>
       <c r="F29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G29" t="n">
-        <v>0.543</v>
+        <v>0.556</v>
       </c>
       <c r="H29" t="n">
         <v>48.4</v>
@@ -5593,7 +5660,7 @@
         <v>37.4</v>
       </c>
       <c r="J29" t="n">
-        <v>81.5</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="K29" t="n">
         <v>0.459</v>
@@ -5602,7 +5669,7 @@
         <v>7.7</v>
       </c>
       <c r="M29" t="n">
-        <v>18.2</v>
+        <v>18.1</v>
       </c>
       <c r="N29" t="n">
         <v>0.423</v>
@@ -5614,13 +5681,13 @@
         <v>20</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="R29" t="n">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="S29" t="n">
-        <v>30.6</v>
+        <v>30.7</v>
       </c>
       <c r="T29" t="n">
         <v>40.6</v>
@@ -5629,43 +5696,43 @@
         <v>22.8</v>
       </c>
       <c r="V29" t="n">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="W29" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="X29" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="Y29" t="n">
         <v>4.4</v>
       </c>
       <c r="Z29" t="n">
-        <v>20</v>
+        <v>20.2</v>
       </c>
       <c r="AA29" t="n">
-        <v>17.9</v>
+        <v>17.8</v>
       </c>
       <c r="AB29" t="n">
         <v>98.59999999999999</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="AD29" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AE29" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AF29" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AG29" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AH29" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI29" t="n">
         <v>9</v>
@@ -5677,7 +5744,7 @@
         <v>10</v>
       </c>
       <c r="AL29" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AM29" t="n">
         <v>14</v>
@@ -5695,7 +5762,7 @@
         <v>2</v>
       </c>
       <c r="AR29" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AS29" t="n">
         <v>15</v>
@@ -5713,13 +5780,13 @@
         <v>20</v>
       </c>
       <c r="AX29" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AY29" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ29" t="n">
         <v>8</v>
-      </c>
-      <c r="AZ29" t="n">
-        <v>6</v>
       </c>
       <c r="BA29" t="n">
         <v>30</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>2-1-2007-08</t>
+          <t>2008-02-01</t>
         </is>
       </c>
     </row>
@@ -5757,88 +5824,88 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E30" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F30" t="n">
         <v>18</v>
       </c>
       <c r="G30" t="n">
-        <v>0.617</v>
+        <v>0.609</v>
       </c>
       <c r="H30" t="n">
         <v>48</v>
       </c>
       <c r="I30" t="n">
-        <v>39.6</v>
+        <v>39.7</v>
       </c>
       <c r="J30" t="n">
-        <v>80.59999999999999</v>
+        <v>80.5</v>
       </c>
       <c r="K30" t="n">
-        <v>0.492</v>
+        <v>0.493</v>
       </c>
       <c r="L30" t="n">
         <v>4.1</v>
       </c>
       <c r="M30" t="n">
-        <v>11.6</v>
+        <v>11.4</v>
       </c>
       <c r="N30" t="n">
-        <v>0.357</v>
+        <v>0.356</v>
       </c>
       <c r="O30" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="P30" t="n">
-        <v>28.6</v>
+        <v>28.8</v>
       </c>
       <c r="Q30" t="n">
         <v>0.753</v>
       </c>
       <c r="R30" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="S30" t="n">
         <v>29</v>
       </c>
       <c r="T30" t="n">
-        <v>40.6</v>
+        <v>40.4</v>
       </c>
       <c r="U30" t="n">
-        <v>26.1</v>
+        <v>26</v>
       </c>
       <c r="V30" t="n">
         <v>15.2</v>
       </c>
       <c r="W30" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="X30" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="Y30" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="Z30" t="n">
-        <v>24.8</v>
+        <v>24.7</v>
       </c>
       <c r="AA30" t="n">
-        <v>23.1</v>
+        <v>23.3</v>
       </c>
       <c r="AB30" t="n">
-        <v>105</v>
+        <v>105.2</v>
       </c>
       <c r="AC30" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AD30" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE30" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF30" t="n">
         <v>8</v>
@@ -5856,7 +5923,7 @@
         <v>15</v>
       </c>
       <c r="AK30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AL30" t="n">
         <v>28</v>
@@ -5865,10 +5932,10 @@
         <v>30</v>
       </c>
       <c r="AN30" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AO30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AP30" t="n">
         <v>5</v>
@@ -5877,13 +5944,13 @@
         <v>16</v>
       </c>
       <c r="AR30" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AS30" t="n">
         <v>28</v>
       </c>
       <c r="AT30" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AU30" t="n">
         <v>2</v>
@@ -5895,22 +5962,22 @@
         <v>2</v>
       </c>
       <c r="AX30" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AY30" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AZ30" t="n">
         <v>30</v>
       </c>
       <c r="BA30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BB30" t="n">
         <v>5</v>
       </c>
       <c r="BC30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BD30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>2-1-2007-08</t>
+          <t>2008-02-01</t>
         </is>
       </c>
     </row>
@@ -5939,43 +6006,43 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E31" t="n">
         <v>24</v>
       </c>
       <c r="F31" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G31" t="n">
-        <v>0.533</v>
+        <v>0.545</v>
       </c>
       <c r="H31" t="n">
         <v>48.6</v>
       </c>
       <c r="I31" t="n">
-        <v>36.3</v>
+        <v>36.5</v>
       </c>
       <c r="J31" t="n">
-        <v>81.5</v>
+        <v>81.7</v>
       </c>
       <c r="K31" t="n">
-        <v>0.445</v>
+        <v>0.446</v>
       </c>
       <c r="L31" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="M31" t="n">
         <v>19.4</v>
       </c>
       <c r="N31" t="n">
-        <v>0.343</v>
+        <v>0.347</v>
       </c>
       <c r="O31" t="n">
-        <v>19.5</v>
+        <v>19.3</v>
       </c>
       <c r="P31" t="n">
-        <v>24.6</v>
+        <v>24.3</v>
       </c>
       <c r="Q31" t="n">
         <v>0.795</v>
@@ -5984,13 +6051,13 @@
         <v>12.2</v>
       </c>
       <c r="S31" t="n">
-        <v>30.4</v>
+        <v>30.5</v>
       </c>
       <c r="T31" t="n">
         <v>42.6</v>
       </c>
       <c r="U31" t="n">
-        <v>19.2</v>
+        <v>19.4</v>
       </c>
       <c r="V31" t="n">
         <v>14</v>
@@ -5999,31 +6066,31 @@
         <v>7.7</v>
       </c>
       <c r="X31" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="Y31" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Z31" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="AA31" t="n">
-        <v>20.1</v>
+        <v>19.9</v>
       </c>
       <c r="AB31" t="n">
-        <v>98.7</v>
+        <v>99</v>
       </c>
       <c r="AC31" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="AD31" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AE31" t="n">
         <v>16</v>
       </c>
       <c r="AF31" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AG31" t="n">
         <v>16</v>
@@ -6032,16 +6099,16 @@
         <v>4</v>
       </c>
       <c r="AI31" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AJ31" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AK31" t="n">
         <v>20</v>
       </c>
       <c r="AL31" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AM31" t="n">
         <v>10</v>
@@ -6059,34 +6126,34 @@
         <v>3</v>
       </c>
       <c r="AR31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AS31" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AT31" t="n">
         <v>10</v>
       </c>
       <c r="AU31" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AV31" t="n">
         <v>9</v>
       </c>
       <c r="AW31" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AX31" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AY31" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AZ31" t="n">
         <v>5</v>
       </c>
       <c r="BA31" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="BB31" t="n">
         <v>13</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>2-1-2007-08</t>
+          <t>2008-02-01</t>
         </is>
       </c>
     </row>
